--- a/danh_sach_thiet_bi_khu_C.xlsx
+++ b/danh_sach_thiet_bi_khu_C.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="234">
   <si>
     <t>Mã Serial</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Treo tường đối diện giường ngủ</t>
   </si>
   <si>
-    <t>Trang bị mới Block C - Tầng 1</t>
+    <t>Trang bị Block C - Tầng 1</t>
   </si>
   <si>
     <t>BOX-C141</t>
@@ -59,9 +59,6 @@
     <t>Gắn sau Tivi / Kệ Tivi</t>
   </si>
   <si>
-    <t>Trang bị Block C - Tầng 1</t>
-  </si>
-  <si>
     <t>RMT-C141</t>
   </si>
   <si>
@@ -71,6 +68,18 @@
     <t>Bàn đầu giường</t>
   </si>
   <si>
+    <t>TEL-C141</t>
+  </si>
+  <si>
+    <t>Điện thoại bàn Panasonic KX-TS500</t>
+  </si>
+  <si>
+    <t>Bàn làm việc / Táp đầu giường</t>
+  </si>
+  <si>
+    <t>Điện thoại bàn nội bộ buồng phòng - Tầng 1</t>
+  </si>
+  <si>
     <t>WF-C141</t>
   </si>
   <si>
@@ -92,6 +101,9 @@
     <t>RMT-C143</t>
   </si>
   <si>
+    <t>TEL-C143</t>
+  </si>
+  <si>
     <t>WF-C143</t>
   </si>
   <si>
@@ -104,6 +116,9 @@
     <t>RMT-C145</t>
   </si>
   <si>
+    <t>TEL-C145</t>
+  </si>
+  <si>
     <t>WF-C145</t>
   </si>
   <si>
@@ -116,6 +131,9 @@
     <t>RMT-C147</t>
   </si>
   <si>
+    <t>TEL-C147</t>
+  </si>
+  <si>
     <t>WF-C147</t>
   </si>
   <si>
@@ -128,6 +146,9 @@
     <t>RMT-C149</t>
   </si>
   <si>
+    <t>TEL-C149</t>
+  </si>
+  <si>
     <t>WF-C149</t>
   </si>
   <si>
@@ -140,6 +161,9 @@
     <t>RMT-C151</t>
   </si>
   <si>
+    <t>TEL-C151</t>
+  </si>
+  <si>
     <t>WF-C151</t>
   </si>
   <si>
@@ -152,6 +176,9 @@
     <t>RMT-C153</t>
   </si>
   <si>
+    <t>TEL-C153</t>
+  </si>
+  <si>
     <t>WF-C153</t>
   </si>
   <si>
@@ -164,6 +191,12 @@
     <t>RMT-C241</t>
   </si>
   <si>
+    <t>TEL-C241</t>
+  </si>
+  <si>
+    <t>Điện thoại bàn nội bộ buồng phòng - Tầng 2</t>
+  </si>
+  <si>
     <t>WF-C241</t>
   </si>
   <si>
@@ -185,6 +218,9 @@
     <t>RMT-C243</t>
   </si>
   <si>
+    <t>TEL-C243</t>
+  </si>
+  <si>
     <t>WF-C243</t>
   </si>
   <si>
@@ -200,6 +236,9 @@
     <t>RMT-C245</t>
   </si>
   <si>
+    <t>TEL-C245</t>
+  </si>
+  <si>
     <t>WF-C245</t>
   </si>
   <si>
@@ -215,6 +254,9 @@
     <t>RMT-C247</t>
   </si>
   <si>
+    <t>TEL-C247</t>
+  </si>
+  <si>
     <t>WF-C247</t>
   </si>
   <si>
@@ -227,6 +269,9 @@
     <t>RMT-C249</t>
   </si>
   <si>
+    <t>TEL-C249</t>
+  </si>
+  <si>
     <t>WF-C249</t>
   </si>
   <si>
@@ -242,6 +287,9 @@
     <t>RMT-C251</t>
   </si>
   <si>
+    <t>TEL-C251</t>
+  </si>
+  <si>
     <t>WF-C251</t>
   </si>
   <si>
@@ -254,6 +302,9 @@
     <t>RMT-C253</t>
   </si>
   <si>
+    <t>TEL-C253</t>
+  </si>
+  <si>
     <t>WF-C253</t>
   </si>
   <si>
@@ -266,6 +317,12 @@
     <t>RMT-C341</t>
   </si>
   <si>
+    <t>TEL-C341</t>
+  </si>
+  <si>
+    <t>Điện thoại bàn nội bộ buồng phòng - Tầng 3</t>
+  </si>
+  <si>
     <t>WF-C341</t>
   </si>
   <si>
@@ -278,6 +335,9 @@
     <t>RMT-C343</t>
   </si>
   <si>
+    <t>TEL-C343</t>
+  </si>
+  <si>
     <t>WF-C343</t>
   </si>
   <si>
@@ -287,6 +347,9 @@
     <t>RMT-C345</t>
   </si>
   <si>
+    <t>TEL-C345</t>
+  </si>
+  <si>
     <t>WF-C345</t>
   </si>
   <si>
@@ -296,6 +359,9 @@
     <t>RMT-C347</t>
   </si>
   <si>
+    <t>TEL-C347</t>
+  </si>
+  <si>
     <t>WF-C347</t>
   </si>
   <si>
@@ -305,6 +371,9 @@
     <t>RMT-C349</t>
   </si>
   <si>
+    <t>TEL-C349</t>
+  </si>
+  <si>
     <t>WF-C349</t>
   </si>
   <si>
@@ -320,12 +389,18 @@
     <t>RMT-C351</t>
   </si>
   <si>
+    <t>TEL-C351</t>
+  </si>
+  <si>
     <t>WF-C351</t>
   </si>
   <si>
     <t>RMT-C353</t>
   </si>
   <si>
+    <t>TEL-C353</t>
+  </si>
+  <si>
     <t>WF-C353</t>
   </si>
   <si>
@@ -338,6 +413,12 @@
     <t>RMT-C441</t>
   </si>
   <si>
+    <t>TEL-C441</t>
+  </si>
+  <si>
+    <t>Điện thoại bàn nội bộ buồng phòng - Tầng 4</t>
+  </si>
+  <si>
     <t>WF-C441</t>
   </si>
   <si>
@@ -350,6 +431,9 @@
     <t>RMT-C443</t>
   </si>
   <si>
+    <t>TEL-C443</t>
+  </si>
+  <si>
     <t>WF-C443</t>
   </si>
   <si>
@@ -359,6 +443,9 @@
     <t>RMT-C445</t>
   </si>
   <si>
+    <t>TEL-C445</t>
+  </si>
+  <si>
     <t>WF-C445</t>
   </si>
   <si>
@@ -374,6 +461,9 @@
     <t>RMT-C447</t>
   </si>
   <si>
+    <t>TEL-C447</t>
+  </si>
+  <si>
     <t>WF-C447</t>
   </si>
   <si>
@@ -386,6 +476,9 @@
     <t>RMT-C449</t>
   </si>
   <si>
+    <t>TEL-C449</t>
+  </si>
+  <si>
     <t>WF-C449</t>
   </si>
   <si>
@@ -398,6 +491,9 @@
     <t>RMT-C451</t>
   </si>
   <si>
+    <t>TEL-C451</t>
+  </si>
+  <si>
     <t>WF-C451</t>
   </si>
   <si>
@@ -410,6 +506,9 @@
     <t>RMT-C453</t>
   </si>
   <si>
+    <t>TEL-C453</t>
+  </si>
+  <si>
     <t>WF-C453</t>
   </si>
   <si>
@@ -422,6 +521,12 @@
     <t>RMT-C541</t>
   </si>
   <si>
+    <t>TEL-C541</t>
+  </si>
+  <si>
+    <t>Điện thoại bàn nội bộ buồng phòng - Tầng 5</t>
+  </si>
+  <si>
     <t>WF-C541</t>
   </si>
   <si>
@@ -434,6 +539,9 @@
     <t>RMT-C543</t>
   </si>
   <si>
+    <t>TEL-C543</t>
+  </si>
+  <si>
     <t>WF-C543</t>
   </si>
   <si>
@@ -443,6 +551,9 @@
     <t>RMT-C545</t>
   </si>
   <si>
+    <t>TEL-C545</t>
+  </si>
+  <si>
     <t>WF-C545</t>
   </si>
   <si>
@@ -452,6 +563,9 @@
     <t>RMT-C547</t>
   </si>
   <si>
+    <t>TEL-C547</t>
+  </si>
+  <si>
     <t>WF-C547</t>
   </si>
   <si>
@@ -461,6 +575,9 @@
     <t>RMT-C549</t>
   </si>
   <si>
+    <t>TEL-C549</t>
+  </si>
+  <si>
     <t>WF-C549</t>
   </si>
   <si>
@@ -470,6 +587,9 @@
     <t>RMT-C551</t>
   </si>
   <si>
+    <t>TEL-C551</t>
+  </si>
+  <si>
     <t>WF-C551</t>
   </si>
   <si>
@@ -479,6 +599,9 @@
     <t>RMT-C553</t>
   </si>
   <si>
+    <t>TEL-C553</t>
+  </si>
+  <si>
     <t>WF-C553</t>
   </si>
   <si>
@@ -491,6 +614,12 @@
     <t>RMT-C641</t>
   </si>
   <si>
+    <t>TEL-C641</t>
+  </si>
+  <si>
+    <t>Điện thoại bàn nội bộ buồng phòng - Tầng 6</t>
+  </si>
+  <si>
     <t>WF-C641</t>
   </si>
   <si>
@@ -509,6 +638,9 @@
     <t>RMT-C643</t>
   </si>
   <si>
+    <t>TEL-C643</t>
+  </si>
+  <si>
     <t>WF-C643</t>
   </si>
   <si>
@@ -518,6 +650,9 @@
     <t>RMT-C645</t>
   </si>
   <si>
+    <t>TEL-C645</t>
+  </si>
+  <si>
     <t>WF-C645</t>
   </si>
   <si>
@@ -533,6 +668,9 @@
     <t>RMT-C647</t>
   </si>
   <si>
+    <t>TEL-C647</t>
+  </si>
+  <si>
     <t>WF-C647</t>
   </si>
   <si>
@@ -545,6 +683,9 @@
     <t>RMT-C649</t>
   </si>
   <si>
+    <t>TEL-C649</t>
+  </si>
+  <si>
     <t>WF-C649</t>
   </si>
   <si>
@@ -557,6 +698,9 @@
     <t>RMT-C651</t>
   </si>
   <si>
+    <t>TEL-C651</t>
+  </si>
+  <si>
     <t>WF-C651</t>
   </si>
   <si>
@@ -567,6 +711,9 @@
   </si>
   <si>
     <t>RMT-C653</t>
+  </si>
+  <si>
+    <t>TEL-C653</t>
   </si>
   <si>
     <t>WF-C653</t>
@@ -946,11 +1093,11 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="36.42" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="39.99" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="18.71" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="36.42" bestFit="true" customWidth="true" style="0"/>
@@ -1014,15 +1161,15 @@
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="C4" s="3">
         <v>141</v>
@@ -1031,18 +1178,18 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="C5" s="3">
         <v>141</v>
@@ -1051,38 +1198,38 @@
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C6" s="3">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3">
         <v>143</v>
@@ -1091,18 +1238,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3">
         <v>143</v>
@@ -1111,18 +1258,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3">
         <v>143</v>
@@ -1131,58 +1278,58 @@
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3">
         <v>145</v>
@@ -1191,18 +1338,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3">
         <v>145</v>
@@ -1211,27 +1358,27 @@
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
@@ -1239,50 +1386,50 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C17" s="3">
         <v>147</v>
@@ -1291,27 +1438,27 @@
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>10</v>
@@ -1319,73 +1466,73 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="3">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>8</v>
@@ -1399,13 +1546,13 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="3">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>8</v>
@@ -1414,187 +1561,187 @@
         <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="3">
+        <v>149</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="3">
-        <v>151</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3">
+        <v>149</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="3">
-        <v>151</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C26" s="3">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C27" s="3">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C28" s="3">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C29" s="3">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C30" s="3">
-        <v>241</v>
+        <v>151</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C31" s="3">
-        <v>241</v>
+        <v>151</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C32" s="3">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1602,159 +1749,159 @@
         <v>51</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C33" s="3">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C34" s="3">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C35" s="3">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C36" s="3">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C37" s="3">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C38" s="3">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C39" s="3">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="3">
+        <v>241</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="3">
-        <v>245</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1765,27 +1912,27 @@
         <v>7</v>
       </c>
       <c r="C41" s="3">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="3">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>8</v>
@@ -1794,298 +1941,298 @@
         <v>13</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="3">
+        <v>243</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="3">
-        <v>247</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="3">
+        <v>243</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="3">
-        <v>247</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C45" s="3">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C46" s="3">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C47" s="3">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C48" s="3">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C49" s="3">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C50" s="3">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C51" s="3">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C52" s="3">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C53" s="3">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C54" s="3">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C55" s="3">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C56" s="3">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="3">
-        <v>341</v>
+        <v>249</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>8</v>
@@ -2094,47 +2241,47 @@
         <v>13</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="3">
+        <v>249</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="3">
-        <v>341</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="3">
+        <v>249</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C59" s="3">
-        <v>341</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F59" s="2" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2142,19 +2289,19 @@
         <v>85</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C60" s="3">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2162,236 +2309,236 @@
         <v>86</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C61" s="3">
-        <v>343</v>
+        <v>251</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C62" s="3">
-        <v>343</v>
+        <v>251</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C63" s="3">
-        <v>345</v>
+        <v>251</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C64" s="3">
-        <v>345</v>
+        <v>251</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C65" s="3">
-        <v>345</v>
+        <v>251</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C66" s="3">
-        <v>347</v>
+        <v>253</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C67" s="3">
-        <v>347</v>
+        <v>253</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C68" s="3">
-        <v>347</v>
+        <v>253</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C69" s="3">
-        <v>349</v>
+        <v>253</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C70" s="3">
-        <v>349</v>
+        <v>253</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C71" s="3">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C72" s="3">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>98</v>
@@ -2399,302 +2546,302 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C73" s="3">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C74" s="3">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C75" s="3">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="3">
+        <v>343</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C76" s="3">
-        <v>353</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F76" s="2" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="3">
+        <v>343</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C77" s="3">
-        <v>353</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F77" s="2" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C78" s="3">
-        <v>441</v>
+        <v>343</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C79" s="3">
-        <v>441</v>
+        <v>345</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C80" s="3">
-        <v>441</v>
+        <v>345</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C81" s="3">
-        <v>443</v>
+        <v>345</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C82" s="3">
-        <v>443</v>
+        <v>345</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C83" s="3">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C84" s="3">
-        <v>445</v>
+        <v>347</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C85" s="3">
-        <v>445</v>
+        <v>347</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C86" s="3">
-        <v>445</v>
+        <v>347</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C87" s="3">
-        <v>447</v>
+        <v>349</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2702,19 +2849,19 @@
         <v>117</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C88" s="3">
-        <v>447</v>
+        <v>349</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2722,19 +2869,19 @@
         <v>118</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C89" s="3">
-        <v>447</v>
+        <v>349</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -2742,19 +2889,19 @@
         <v>119</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C90" s="3">
-        <v>447</v>
+        <v>349</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2765,27 +2912,27 @@
         <v>7</v>
       </c>
       <c r="C91" s="3">
-        <v>449</v>
+        <v>351</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C92" s="3">
-        <v>449</v>
+        <v>351</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>8</v>
@@ -2794,67 +2941,67 @@
         <v>13</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" s="3">
+        <v>351</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C93" s="3">
-        <v>449</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F93" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" s="3">
+        <v>351</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C94" s="3">
-        <v>449</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F94" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C95" s="3">
-        <v>451</v>
+        <v>351</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2862,19 +3009,19 @@
         <v>126</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="3">
+        <v>353</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C96" s="3">
-        <v>451</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F96" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2882,19 +3029,19 @@
         <v>127</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="3">
+        <v>353</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C97" s="3">
-        <v>451</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F97" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2902,19 +3049,19 @@
         <v>128</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C98" s="3">
-        <v>453</v>
+        <v>353</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2925,7 +3072,7 @@
         <v>12</v>
       </c>
       <c r="C99" s="3">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>8</v>
@@ -2934,124 +3081,124 @@
         <v>13</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="3">
+        <v>441</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" s="3">
-        <v>453</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C101" s="3">
+        <v>441</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C101" s="3">
-        <v>453</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F101" s="2" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C102" s="3">
-        <v>541</v>
+        <v>441</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C103" s="3">
-        <v>541</v>
+        <v>443</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C104" s="3">
-        <v>541</v>
+        <v>443</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C105" s="3">
-        <v>543</v>
+        <v>443</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>133</v>
@@ -3059,79 +3206,79 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C106" s="3">
-        <v>543</v>
+        <v>443</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C107" s="3">
-        <v>543</v>
+        <v>445</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C108" s="3">
-        <v>545</v>
+        <v>445</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C109" s="3">
-        <v>545</v>
+        <v>445</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>133</v>
@@ -3139,99 +3286,99 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C110" s="3">
-        <v>545</v>
+        <v>445</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C111" s="3">
-        <v>547</v>
+        <v>447</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C112" s="3">
-        <v>547</v>
+        <v>447</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C113" s="3">
-        <v>547</v>
+        <v>447</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C114" s="3">
-        <v>549</v>
+        <v>447</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>133</v>
@@ -3239,53 +3386,53 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C115" s="3">
-        <v>549</v>
+        <v>447</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C116" s="3">
-        <v>549</v>
+        <v>449</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C117" s="3">
-        <v>551</v>
+        <v>449</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>8</v>
@@ -3294,187 +3441,187 @@
         <v>13</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C118" s="3">
+        <v>449</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C118" s="3">
-        <v>551</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F118" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B119" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C119" s="3">
+        <v>449</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C119" s="3">
-        <v>551</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F119" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C120" s="3">
-        <v>553</v>
+        <v>449</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C121" s="3">
-        <v>553</v>
+        <v>451</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C122" s="3">
-        <v>553</v>
+        <v>451</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C123" s="3">
-        <v>641</v>
+        <v>451</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C124" s="3">
-        <v>641</v>
+        <v>451</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C125" s="3">
-        <v>641</v>
+        <v>453</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C126" s="3">
-        <v>643</v>
+        <v>453</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3482,19 +3629,19 @@
         <v>162</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C127" s="3">
-        <v>643</v>
+        <v>453</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3502,19 +3649,19 @@
         <v>163</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C128" s="3">
-        <v>643</v>
+        <v>453</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3522,19 +3669,19 @@
         <v>164</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C129" s="3">
-        <v>643</v>
+        <v>453</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3545,7 +3692,7 @@
         <v>12</v>
       </c>
       <c r="C130" s="3">
-        <v>645</v>
+        <v>541</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>8</v>
@@ -3554,78 +3701,78 @@
         <v>13</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C131" s="3">
+        <v>541</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" s="3">
-        <v>645</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C132" s="3">
+        <v>541</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C132" s="3">
-        <v>645</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F132" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C133" s="3">
-        <v>647</v>
+        <v>541</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C134" s="3">
-        <v>647</v>
+        <v>543</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>8</v>
@@ -3634,78 +3781,78 @@
         <v>13</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C135" s="3">
+        <v>543</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C135" s="3">
-        <v>647</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F135" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B136" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C136" s="3">
+        <v>543</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C136" s="3">
-        <v>647</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F136" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C137" s="3">
-        <v>649</v>
+        <v>543</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C138" s="3">
-        <v>649</v>
+        <v>545</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>8</v>
@@ -3714,78 +3861,78 @@
         <v>13</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" s="3">
+        <v>545</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C139" s="3">
-        <v>649</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F139" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B140" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C140" s="3">
+        <v>545</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C140" s="3">
-        <v>649</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F140" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C141" s="3">
-        <v>651</v>
+        <v>545</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C142" s="3">
-        <v>651</v>
+        <v>547</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>8</v>
@@ -3794,78 +3941,78 @@
         <v>13</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" s="3">
+        <v>547</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C143" s="3">
-        <v>651</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F143" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C144" s="3">
+        <v>547</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C144" s="3">
-        <v>651</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F144" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C145" s="3">
-        <v>653</v>
+        <v>547</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C146" s="3">
-        <v>653</v>
+        <v>549</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>8</v>
@@ -3874,47 +4021,887 @@
         <v>13</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C147" s="3">
+        <v>549</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C147" s="3">
-        <v>653</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F147" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C148" s="3">
+        <v>549</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C148" s="3">
+      <c r="F148" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C149" s="3">
+        <v>549</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C150" s="3">
+        <v>551</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C151" s="3">
+        <v>551</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C152" s="3">
+        <v>551</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C153" s="3">
+        <v>551</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C154" s="3">
+        <v>553</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" s="3">
+        <v>553</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C156" s="3">
+        <v>553</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C157" s="3">
+        <v>553</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C158" s="3">
+        <v>641</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C159" s="3">
+        <v>641</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C160" s="3">
+        <v>641</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C161" s="3">
+        <v>641</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="3">
+        <v>643</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C163" s="3">
+        <v>643</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C164" s="3">
+        <v>643</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C165" s="3">
+        <v>643</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C166" s="3">
+        <v>643</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C167" s="3">
+        <v>645</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C168" s="3">
+        <v>645</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C169" s="3">
+        <v>645</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C170" s="3">
+        <v>645</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" s="3">
+        <v>647</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C172" s="3">
+        <v>647</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173" s="3">
+        <v>647</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C174" s="3">
+        <v>647</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C175" s="3">
+        <v>647</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" s="3">
+        <v>649</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C177" s="3">
+        <v>649</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" s="3">
+        <v>649</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C179" s="3">
+        <v>649</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C180" s="3">
+        <v>649</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" s="3">
+        <v>651</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C182" s="3">
+        <v>651</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C183" s="3">
+        <v>651</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C184" s="3">
+        <v>651</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C185" s="3">
+        <v>651</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C186" s="3">
         <v>653</v>
       </c>
-      <c r="D148" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>159</v>
+      <c r="D186" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C187" s="3">
+        <v>653</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C188" s="3">
+        <v>653</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C189" s="3">
+        <v>653</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C190" s="3">
+        <v>653</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
